--- a/eval/RBI_NBFC_Retrieval_Questions_results_v2.xlsx
+++ b/eval/RBI_NBFC_Retrieval_Questions_results_v2.xlsx
@@ -512,7 +512,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>The asset-size threshold generally placing a non-deposit-taking NBFC-ICC in the Middle Layer is ₹1,000 crore **on a standalone basis** [3]. However, if the NBFC-ICC is part of a group, its classification depends on the **consolidated asset size of the entire group**. For example, if the group’s consolidated assets exceed ₹1,000 crore, the NBFC-ICC is classified in the Middle Layer even if its standalone asset size is below ₹1,000 crore [1][5]. This consolidated threshold applies to groups where multiple NBFCs are part of a common Group or floated by common promoters [17]. Additionally, once an NBFC reaches ₹1,000 crore in asset size (standalone or consolidated), it is subject to Middle Layer regulatory requirements [4][22].</t>
+          <t>The asset-size threshold that generally places a non-deposit-taking NBFC-ICC in the Middle Layer is ₹1,000 crore. This is explicitly stated in [3], which defines the Middle Layer as including "non-deposit taking NBFCs with asset size of ₹1,000 crore and above." However, for NBFCs in a group, the consolidated asset size of the entire group determines classification, as explained in [1] and [5]. If the group's consolidated assets exceed ₹1,000 crore, NBFC-ICC and NBFC-MFI are classified in the Middle Layer even if their standalone asset size is below ₹1,000 crore.</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -531,7 +531,7 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>13</v>
+        <v>11.8</v>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
@@ -566,11 +566,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Under the 2025 NOF transition schedule, existing NBFC-ICC must achieve a minimum net owned fund (NOF) of ₹5 crore by March 31, 2025, and ₹10 crore by March 31, 2027 [1]. 
-Conditions:  
-- NBFC-ICC with current NOF of ₹2 crore must incrementally reach ₹5 crore by 2025 and ₹10 crore by 2027.  
-- Failure to meet these milestones by the stipulated dates disqualifies NBFCs from holding the Certificate of Registration (CoR) [1].  
-- The glide path applies to NBFC-ICC, NBFC-MFI (excluding North East Region distinctions), and NBFC-Factor [1].</t>
+          <t>Under the 2025 NOF transition schedule, an existing NBFC-ICC must achieve a minimum net owned fund (NOF) of ₹5 crore by March 31, 2025 [1]. This is part of a glide path where NBFC-ICC currently have a NOF of ₹2 crore and are required to progressively increase it to ₹10 crore by March 31, 2027 [1]. Failure to meet these targets would result in ineligibility to hold the Certificate of Registration (CoR) as an NBFC [1].</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -580,16 +576,16 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>all key figures present (5crore, 31, 2025, 10crore, 2027.)</t>
+          <t>found 5crore, 31, 2025, 10crore; missing 2027.</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>21.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
@@ -624,7 +620,10 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>The minimum CRAR for a Middle Layer NBFC-ICC (not primarily a gold lender) is 15% of aggregate RWAs, and the minimum Tier 1 capital ratio is 10% of aggregate RWAs [2]. The Tier 2 capital of the NBFC shall not exceed 100% of Tier 1 capital [2]. These requirements apply to NBFC-ML (Middle Layer) and above, and NBFC-ICC falls under this category. No additional thresholds or exceptions are specified for NBFC-ICC in the passages.</t>
+          <t>The minimum CRAR and Tier 1 capital ratios for a Middle Layer NBFC-ICC that is not primarily a gold lender are as follows:  
+- **Minimum Tier 1 capital**: 10% of the aggregate Risk Weighted Assets (RWAs) [2].  
+- **Minimum CRAR**: 15% of the aggregate RWAs [2].  
+The Tier 2 capital of the NBFC shall not exceed 100% of Tier 1 capital [2]. These requirements apply to NBFC-ML (Middle Layer) and above, and NBFC-ICC falls under this category.</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -643,7 +642,7 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>11.2</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
@@ -678,11 +677,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>The minimum Common Equity Tier 1 (CET1) ratio for an Upper Layer NBFC-ICC is **9 per cent of the aggregate RWAs**, as specified for NBFC-UL (Upper Layer) in [1].  
-**Conditions and exceptions**:  
-- This requirement applies to NBFCs classified in the Upper Layer of the regulatory structure [1].  
-- NBFC-ICC (Non-Banking Financial Company - Infrastructure Finance Company) is not explicitly mentioned in the passages, but if it falls under the Upper Layer category, the 9% CET1 requirement would apply.  
-- No additional carve-outs or thresholds are specified for NBFC-ICC in the provided contexts.</t>
+          <t>The passages do not specify the minimum Common Equity Tier 1 (CET1) ratio for an Upper Layer NBFC-ICC. The only CET1 requirement mentioned is for NBFC-UL (Upper Layer) in [1], which mandates a minimum CET1 capital of 9% of aggregate RWAs. However, NBFC-ICC (Non-Banking Financial Company - Infrastructure Finance Company) is addressed in [5] only regarding Net Owned Fund (NOF) requirements, not CET1 ratios. Since the passages do not explicitly link NBFC-ICC to CET1 thresholds or clarify its regulatory layer status, the answer cannot be determined from the provided text.</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -692,16 +687,16 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>REVIEW</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>all key figures present (9%)</t>
+          <t>declined to answer an in-scope question - retrieval likely missed</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>9.5</v>
+        <v>9</v>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
@@ -736,7 +731,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>The maximum leverage ratio for a Base Layer NBFC-ICC is seven, as specified in [3]. This applies to all NBFC-BL (Base Layer) entities, including NBFC-ICC, unless there are specific exceptions or sub-rules for NBFC-ICC. No separate leverage ratio is mentioned for NBFC-ICC in the provided passages.</t>
+          <t>The maximum leverage ratio for a Base Layer NBFC-ICC is seven, as stipulated in [3]. This applies because NBFC-ICC registered under the RBI Act, 1934, falls under the Base Layer category, and the leverage ratio for NBFC-BL (Base Layer) is explicitly capped at seven [3].</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -755,7 +750,7 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>11.7</v>
+        <v>10.1</v>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
@@ -790,12 +785,11 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>The standard periodic KYC update intervals are: **high-risk customers every 2 years**, **medium-risk customers every 8 years**, and **low-risk customers every 10 years** from the date of account opening or last KYC updation [1].  
-**Conditions and exceptions**:  
-1. For **low-risk individual customers**, if KYC updation is due, the NBFC must complete it within **1 year of the due date** or by **June 30, 2026**, whichever is later [1](2).  
-2. The NBFC must document its policy for these intervals in its internal KYC policy, approved by the Board of Directors or a delegated committee [1](1).  
-3. For **non-individual customers**, the intervals follow the same risk-based framework but require additional verification steps for changes in KYC information [1](4)(ii).  
-4. If CDD documents expire during periodic updation, the NBFC must redo KYC as per new customer onboarding standards [1](5)(i).</t>
+          <t>The standard periodic KYC update intervals for customers are:  
+- **High-risk customers**: At least once every **2 years** [1].  
+- **Medium-risk customers**: At least once every **8 years** [1].  
+- **Low-risk customers**: At least once every **10 years** [1].  
+These intervals apply from the date of account opening or the last KYC updation. For low-risk individual customers, an exception allows updates within **1 year of the due date** or by **June 30, 2026**, whichever is later [1](2).</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -814,7 +808,7 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>8.5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
@@ -849,12 +843,10 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>The transaction records must be retained for at least five years from the date of the transaction [3](47(1)), and customer identification records, including addresses, must be preserved for five years after the business relationship ends [3](47(2)). 
-**Conditions and limits:**  
-- The retention applies to both domestic and international transactions [3](47(1)).  
-- Records must be maintained in hard or soft format and easily retrievable [3](47(6)).  
-- For non-profit organizations, registration details must be kept for five years post-account closure or relationship end, whichever is later [3](48).  
-- Periodic updation of KYC data is required every 2, 8, or 10 years based on risk categorization [4](42(1)), but this does not affect the retention period for records.</t>
+          <t>The transaction records and customer identification records must be retained for **five years** under the KYC directions. Specifically:  
+- **Transaction records** must be maintained for at least **five years from the date of the transaction** [3].  
+- **Customer identification and address records** must be preserved for **five years after the business relationship has ended** [3].  
+These requirements are outlined in Chapter VII - Record Management (paragraph 47) of the directions.</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -873,7 +865,7 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>7.8</v>
+        <v>6.1</v>
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
@@ -908,11 +900,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>For an ordinary term loan at a Middle Layer NBFC-ICC, the overdue period triggering NPA classification is **more than 90 days**, as specified in [3]. This applies to NBFC-ICC granted CoR under the Factoring Regulation Act, 2011, with asset sizes of ₹500 crore and above. The 90-day threshold is effective for these entities, overriding the general 180-day norm for other NBFCs [2]. 
-**Conditions and exceptions**:  
-- The 90-day norm applies only to NBFC-ICC with asset size ≥ ₹500 crore or granted CoR under the Factoring Regulation Act [3].  
-- For NBFC-ML (Middle Layer) not covered under [3], the NPA threshold is **more than 90 days** as per [1], but with a glide path to 90 days by March 31, 2026 [2].  
-- The 90-day rule does not apply to NBFCs already following the 90-day norm [2].</t>
+          <t>For an ordinary term loan at a Middle Layer NBFC-ICC, the overdue period triggering NPA classification is **more than 90 days**, as specified in [3]. This applies to NBFC-ICC (and NBFC-Factors with asset size ₹500 crore or above) granted CoR under the Factoring Regulation Act, 2011. The 90-day threshold is effective for these entities, overriding the general 180-day norm for other NBFCs [3].</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -922,16 +910,16 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>REVIEW</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>declined to answer an in-scope question - retrieval likely missed</t>
+          <t>all key figures present (90days)</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>11.5</v>
+        <v>15.6</v>
       </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
@@ -966,12 +954,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>The standard-asset provision for ordinary loans of a Middle Layer NBFC-ICC (excluding exposures with special provisioning rules) is **0.40 per cent of the outstanding** [1]. This rate applies to all standard assets, including microfinance loans, as explicitly stated in the explanation [1]. 
+          <t>The standard-asset provision applicable to ordinary loans of a Middle Layer NBFC-ICC, excluding exposures with special provisioning rules, is **0.40 per cent of the outstanding**. This rate applies to standard assets as per paragraph 55 of the provisioning requirements [1]. 
 **Conditions and exceptions**:  
-- The 0.40% rate is **not applicable** to NBFC-UL (Upper Layer) or specific loan types like housing loans at teaser rates (2.00% initially, reducing to 0.40% after 1 year if rates reset) or commercial real estate loans [3].  
-- The provision **does not apply** to sub-standard, doubtful, or loss assets, which are governed by separate rates [4].  
-- NBFC-ICC, being part of the Middle Layer, inherits applicability of NBFC-BL provisions unless overridden by specific rules for its category [2].  
-- Exposures to Government entities or certain group investments are exempt from standard provisioning rules [5].</t>
+- The 0.40% rate is explicitly stated for NBFC-ML (Middle Layer) standard assets and includes microfinance loans [1].  
+- For NBFC-UL (Upper Layer), different rates apply (e.g., 0.25% for individual housing loans/SMEs, 2.00% for teaser-rate housing loans, etc.) [3], but NBFC-ICC falls under Middle Layer.  
+- Special provisioning rules (e.g., for project finance, securitisation, or restructured advances) are excluded here [4][3].  
+- The rate is not applicable to NBFC-UL or NBFC-BL (Base Layer) unless specified otherwise [2].</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -990,7 +978,7 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>11.9</v>
+        <v>13.3</v>
       </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
@@ -1025,11 +1013,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Under the 2025 transition schedule, a Base Layer NBFC must move from the 120-day to the 90-day NPA norm by **March 31, 2025**. This is specified in the glide path outlined in paragraph 44 of the Reserve Bank of India (Non-Banking Financial Companies - Income Recognition, Asset Classification and Provisioning) Directions, 2025, which applies to NBFCs transitioning from the 180-day NPA norm to the 90-day norm. The timeline for &gt;120 days overdue is explicitly set as **March 31, 2025** [1]. 
-**Conditions and exceptions**:  
-- This glide path does not apply to NBFCs already required to follow the 90-day NPA norm [1].  
-- The transition applies to all NBFCs, including Base Layer NBFCs, unless otherwise specified [5].  
-- The 90-day norm for NBFCs with asset sizes of ₹500 crore and above is also part of the 2025 Directions, but the specific timeline for the 120-day to 90-day transition is tied to the glide path in paragraph 44 [2].</t>
+          <t>Under the 2025 transition schedule, a Base Layer NBFC must move from the 120-day to the 90-day NPA norm by **March 31, 2025**. This is specified in the glide path outlined in paragraph 44 of the Reserve Bank of India (Non-Banking Financial Companies - Income Recognition, Asset Classification and Provisioning) Directions, 2025, which applies to NBFCs not already following the 90-day norm [1]. The timeline for the 120-day overdue period is explicitly set for March 31, 2025 [1].</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1048,7 +1032,7 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>16.2</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
@@ -1083,7 +1067,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>The provided context passages do not specify the minimum and maximum public-deposit tenors for an eligible deposit-taking NBFC-ICC. The regulations focus on limits on deposit amounts (e.g., one and one-half times NOF [1]), credit ratings [2], compliance with prudential norms [3], NOF requirements [4], and private placement guidelines for NCDs [5], but none address the duration (tenor) of public deposits. Thus, the answer cannot be derived from the given texts.</t>
+          <t>The context passages do not specify the minimum and maximum public-deposit tenors applicable to an eligible deposit-taking NBFC-ICC. The provided information focuses on limits on deposit amounts (e.g., one and one-half times NOF [1]), credit rating requirements [2], auditor reporting obligations [3], NOF thresholds for NBFC categories [4], private placement guidelines for NCDs [5], and applicability of regulations [6]. None of these passages address the duration (tenor) of public deposits.</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1102,7 +1086,7 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>10.8</v>
+        <v>12.2</v>
       </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
@@ -1137,11 +1121,11 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>The public-deposit ceiling for an eligible NBFC-ICC meeting the minimum NOF and prudential requirements is **one and one-half times its Net Owned Fund (NOF)** [1].  
-**Conditions/exceptions**:  
-1. If the NBFC exceeds this limit, it cannot renew or accept fresh deposits until it reaches the revised limit [1].  
-2. Matured public deposits cannot be renewed without the depositor's express and voluntary consent [1].  
-3. The NOF for NBFC-ICC is ₹10 crore, making the deposit ceiling ₹15 crore (1.5 × ₹10 crore) [2].</t>
+          <t>The public-deposit ceiling for an eligible NBFC-ICC meeting the minimum NOF and prudential requirements is **one and one-half times its Net Owned Fund (NOF)** [1]. This means the NBFC-ICC can accept or renew public deposits up to **1.5 × its NOF**. 
+**Conditions and exceptions**:  
+- If the NBFC-ICC holds public deposits exceeding this limit, it **shall not renew or accept fresh deposits** until it reaches the revised limit [1].  
+- **Matured public deposits** cannot be renewed without the **express and voluntary consent of the depositor** [1].  
+- The NOF for NBFC-ICC is **₹10 crore** (as per the glide path in passage [2]), making the ceiling **₹15 crore** (1.5 × ₹10 crore).</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1160,7 +1144,7 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>9.1</v>
+        <v>10.1</v>
       </c>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
@@ -1195,7 +1179,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>The minimum investment-grade credit rating prescribed for public-deposit acceptance is the "minimum investment grade" as specified in the Reserve Bank of India (Non-Banking Financial Companies - Acceptance of Public Deposits) Directions, 2025. However, the exact rating level (e.g., AAA, A, etc.) is not explicitly stated in the provided passages [1][2][3][4][5]. The requirement mandates obtaining such a rating from an approved agency, with downgrading below this threshold triggering specific compliance actions [1][4].</t>
+          <t>The passages do not specify the exact minimum investment-grade credit rating prescribed for public-deposit acceptance. They only state that NBFCs and housing finance companies must obtain "minimum investment grade" from an approved credit rating agency, but no particular rating level (e.g., AAA, BBB) is mentioned [1][2][3][5]. The focus is on compliance with procedural requirements rather than defining the specific credit rating grade.</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1205,16 +1189,16 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>CHECK</t>
+          <t>REVIEW</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>no numeric facts to compare - read the answer yourself</t>
+          <t>declined to answer an in-scope question - retrieval likely missed</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>5.6</v>
+        <v>5.3</v>
       </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
@@ -1247,32 +1231,20 @@
           <t>high</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Recovery calls for overdue loans other than microfinance loans are prohibited outside the hours of **8:00 a.m. to 7:00 p.m.** [1], [2]. Additionally, telemarketing calls are prohibited before **09:30 hours** or after **19:00 hours** unless specifically requested [4]. 
-**Conditions and exceptions:**  
-- The prohibition in [1] and [2] explicitly excludes microfinance loans, which are governed by separate rules [1].  
-- The stricter 09:30–19:00 restriction in [4] applies to telemarketing activities (e.g., DSAs/DMAs) but may overlap with the broader 8:00–7:00 rule.  
-- Calls outside these hours are prohibited unless explicitly authorized or required by law.</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>12942_Responsible-Business-Conduct.pdf p.28 | 12939_Housing-Finance-Companies.pdf p.70 | 12942_Responsible-Business-Conduct.pdf p.27 | 12939_Housing-Finance-Companies.pdf p.59 | 12942_Responsible-Business-Conduct.pdf p.9 | 12939_Housing-Finance-Companies.pdf p.68</t>
-        </is>
-      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>ERROR</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>all key figures present (00)</t>
+          <t>ReadTimeout: timed out</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>29.3</v>
+        <v>300.7</v>
       </c>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
@@ -1307,12 +1279,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>The minimum KFS validity period for retail and MSME term loans is **one working day** for loans with a tenor of **less than seven days**, and **three working days** for loans with a tenor of **seven days or more** [1]. 
-Conditions:  
-- Validity period refers to the time available to the borrower to agree to the loan terms after receiving the KFS [1].  
-- The validity period is **mandatory** for all retail and MSME term loans, except credit card receivables [1].  
-- For loans with a tenor of **seven days or more**, the validity period must be **at least three working days** [1].  
-- For loans with a tenor of **less than seven days**, the validity period is **one working day** [1].</t>
+          <t>The minimum KFS validity period for retail and MSME term loans is **three working days** for loans with a tenor of **seven days or more**, and **one working day** for loans with a tenor of **less than seven days** [1].</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1331,7 +1298,7 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>13.4</v>
+        <v>5.2</v>
       </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
@@ -1366,12 +1333,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>A Middle Layer NBFC-ICC must appoint a Chief Risk Officer (CRO) if its **individual asset size exceeds ₹5,000 crore** [1]. This threshold is explicitly stated in paragraph 19 of [1], which applies to all NBFCs, including NBFC-ICC, regardless of their classification in the Middle Layer. 
-Conditions and exceptions:  
-- The requirement is based on **individual asset size**, not group consolidation [3]. Even if the NBFC-ICC is classified as Middle Layer due to group consolidation (e.g., consolidated assets ≥ ₹1,000 crore), it still must appoint a CRO only if its **own asset size** surpasses ₹5,000 crore.  
-- The CRO must report directly to the MD&amp;CEO/RMCB, have no business targets, and avoid dual roles [1].  
-- Premature transfer/removal of the CRO requires Board approval and reporting to RBI/NHB [1].  
-- The CRO’s role is advisory for credit proposals, focusing on inherent and control risks [1].</t>
+          <t>An NBFC-ICC classified in the Middle Layer must appoint a Chief Risk Officer (CRO) if its asset size exceeds ₹5,000 crore, as per rule 19 of [1]. The Middle Layer classification threshold for NBFC-ICC is ₹1,000 crore [5], but the CRO requirement is triggered independently at ₹5,000 crore [1]. If the NBFC-ICC's standalone asset size is below ₹5,000 crore, it is not mandatorily required to appoint a CRO, even if it is in the Middle Layer due to group consolidation [3][6].</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1390,7 +1352,7 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>8.300000000000001</v>
+        <v>7.5</v>
       </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
@@ -1425,7 +1387,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>A Middle Layer NBFC must submit its quarterly director-change statement and fit-and-proper certificate to the Reserve Bank's Regional Office within **15 days of the close of the respective quarter** [1]. For the quarter ending **March 31**, the statement must be **certified by the auditors** [1]. This requirement applies to all NBFCs under the Directions, including Middle Layer NBFCs, as the applicability of the Directions to Middle Layer NBFCs is explicitly stated in the context [4]. No additional or differing deadlines are specified for Middle Layer NBFCs in the provided passages.</t>
+          <t>A Middle Layer NBFC must submit its quarterly director-change statement and fit-and-proper certificate within **15 days of the close of the respective quarter** [1]. For the quarter ending March 31, the certificate must be **certified by the auditors** [1]. These requirements apply as the Directions governing NBFCs in Middle Layer (and Base Layer) are subject to the general provisions outlined in paragraph 14 of the Governance Directions [4].</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1444,7 +1406,7 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>9.699999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
@@ -1480,7 +1442,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Under the November 28, 2025 version, routine credit-bureau reporting required submissions on reference dates of **9th, 16th, 23rd, and the last day of the month** [1]. For the **full file** (containing all active accounts and accounts with ended relationships since the last reference date), the submission deadline was the **5th day of the next month** [1]. For **incremental accounts** reported on 9th, 16th, and 23rd, submissions were due within **four calendar days** from those dates [1].</t>
+          <t>Under the November 28, 2025 version of the Reserve Bank of India (Non-Banking Financial Companies - Credit Information Reporting) Directions, the reference dates for routine credit-bureau reporting were **9th, 16th, 23rd, and the last day of the month** [1]. For the full file submission, the deadline was **by the 5th day of the next month** [1]. Incremental accounts were to be submitted within **four (4) calendar days** from the reference dates (9th, 16th, and 23rd) [1]. These timelines applied prior to the substitution effective July 1, 2026 [1].</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1499,7 +1461,7 @@
         </is>
       </c>
       <c r="J19" t="n">
-        <v>9.6</v>
+        <v>8.6</v>
       </c>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
@@ -1534,12 +1496,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>The minimum cooling-off period for a digital loan is **one day**, as determined by the NBFC's credit policy, which cannot be less than this duration [1]. 
-**Conditions and exceptions**:  
-- The cooling-off period is determined by the NBFC's board-approved policy but must not be shorter than **one day** [1].  
-- If the borrower exits the loan during this period, the NBFC may retain a reasonable one-time processing fee, provided it is disclosed upfront in the Key Fact Statement (KFS) [1].  
-- For loans transferred to other entities under resolution plans, a **minimum cooling period of 12 months** applies before fresh exposures can be taken on the borrower [4].  
-- Pre-payment beyond the cooling-off period is allowed under the RBI Directions, 2025, without penalty [1].</t>
+          <t>The minimum cooling-off period for a digital loan is **one day**, as determined by the NBFC's credit policy. The borrower can exit the loan during this period by paying the principal and proportionate APR without penalty, and the cooling-off period cannot be less than one day [1].</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1558,7 +1515,7 @@
         </is>
       </c>
       <c r="J20" t="n">
-        <v>8.199999999999999</v>
+        <v>7.1</v>
       </c>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
@@ -1593,14 +1550,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>The percentage cap applicable to default loss guarantee (DLG) cover on an eligible digital-lending portfolio is **5%**, as specified in the following:  
-- The total DLG cover on any outstanding portfolio must not exceed **five per cent of the total amount disbursed** out of that loan portfolio at any given time [3].  
-- DLG provisions under CLA (Credit Linked Assistance) are limited to **five per cent of loans outstanding** [6].  
-**Conditions and exceptions**:  
-1. The DLG cover is calculated based on the disbursed amount, not the total sanctioned loans [3].  
-2. For implicit guarantee arrangements, the DLG provider’s performance risk is capped at **five per cent of the underlying loan portfolio** [3].  
-3. The DLG cover is activated proportionally as loans are disbursed, with the cap applying to the disbursed portion [3].  
-4. Recovery of defaulted loans does not reinstate DLG cover [4].</t>
+          <t>The percentage cap applicable to default loss guarantee (DLG) cover on an eligible digital-lending portfolio is **five per cent** of the total amount disbursed out of that loan portfolio at any given time. This is explicitly stated in [3], which mandates that the total DLG cover on any outstanding portfolio under a DLG arrangement shall not exceed 5% of the total amount disbursed.</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1619,7 +1569,7 @@
         </is>
       </c>
       <c r="J21" t="n">
-        <v>7.3</v>
+        <v>6.2</v>
       </c>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
@@ -1654,12 +1604,12 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>The Base, Middle, Upper, and Top Layers categorize NBFCs based on size, activity, and risk, with distinct regulatory requirements:  
-- **Base Layer (NBFCs-BL)**: NBFCs here have the lowest regulatory burden. Examples include NBFC-P2P, NBFC-AA, NOFHC, and Type I NBFCs [3]. They face a materiality threshold of ₹1 crore for loans to related parties [2], and comply with Chapter III of the Directions [6].  
-- **Middle Layer (NBFCs-ML)**: NBFCs like CIC, NBFC-D, SPD, and IDF-NBFC fall here [3]. They must maintain 10% Tier 1 capital, 15% CRAR, and a materiality threshold of ₹5 crore [2][4]. They follow Chapters II, III, and IV [6].  
-- **Upper Layer (NBFCs-UL)**: NBFCs such as NBFC-D, CIC, NBFC-IFC, and HFC may be placed here [3]. They require 10% Tier 1 capital, 15% CRAR, and a materiality threshold of ₹10 crore [2][4]. They follow Chapters II, III, IV, and V [6].  
-- **Top Layer (NBFCs-TL)**: Ideally empty, but if populated, NBFCs here face higher capital charges (specifically communicated at classification) [1][4]. They would follow stricter regulations than Upper Layer.  
-Each layer’s rules apply based on the NBFC’s last audited balance sheet [2], with exceptions for fixed categories (e.g., NBFC-P2P always in Base Layer) [3].</t>
+          <t>The Base, Middle, Upper, and Top Layers categorize Non-Banking Financial Companies (NBFCs) based on their size, activity, and risk profile under the Scale Based Regulation (SBR) framework [1]. 
+- **Base Layer (NBFCs-BL)**: NBFCs in this layer are smaller, lower-risk entities. They must comply with Chapter III of the regulations [6], and their materiality threshold for loans is ₹1 crore [2]. Examples include NBFC-P2P, NBFC-AA, NOFHC, and Type I NBFCs [3].  
+- **Middle Layer (NBFCs-ML)**: These NBFCs have moderate size and risk. They must follow Chapters II, III, and IV [6], with a materiality threshold of ₹5 crore for loans [2]. Examples include NBFC-D, CIC, NBFC-IFC, HFC, and SPD [3].  
+- **Upper Layer (NBFCs-UL)**: Larger, higher-risk NBFCs in this layer must adhere to Chapters II, III, IV, and V [6], with a materiality threshold of ₹10 crore for loans [2]. Examples include NBFC-Investment, NBFC-MFIs, NBFC-Factors, and MGCs [3].  
+- **Top Layer (NBFCs-TL)**: Ideally empty, this layer would apply to the highest-risk NBFCs, subject to stricter capital requirements (e.g., higher capital charges) [1][4]. Specific criteria for classification here are not detailed in the passages.  
+Each layer’s requirements affect capital adequacy [4], governance [6], and credit risk management [2].</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1678,7 +1628,7 @@
         </is>
       </c>
       <c r="J22" t="n">
-        <v>8.800000000000001</v>
+        <v>8.1</v>
       </c>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
@@ -1713,14 +1663,10 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>If a company does not take customer deposits, it does not automatically mean it does not use public funds, as "public funds" are defined more broadly. According to [1], public funds include funds raised through public deposits, inter-corporate deposits, bank finance, and other sources like Commercial Papers or debentures [1]. Thus, even without customer deposits, a company might still use public funds via these alternative channels. 
-However, if a company **explicitly avoids all public funds** (including indirect receipt through associates or Group entities) and **has no customer interface**, it may qualify as an "NBFC not availing public funds and not having any customer interface" [1]. Such entities can be exempt from certain regulatory requirements, provided they meet specific conditions like asset size limits (₹1,000 crore or less) and annual board resolutions [2]. 
-Key caveats:  
-1. **Public funds** are not limited to customer deposits [1].  
-2. **Indirect receipt** of public funds (e.g., via Group entities) is prohibited [1].  
-3. **Existing unregistered Type I NBFCs** must still comply with other regulatory provisions under Chapter IIIB of the RBI Act [3].  
-4. **Overseas investments** by unregistered Type I NBFCs require registration and stricter oversight [3].  
-Thus, avoiding customer deposits alone does not suffice to exclude public funds; the broader definition must be considered.</t>
+          <t>No, not taking customer deposits does not automatically mean a company does not use public funds. According to the definitions in the passages:  
+- **Public funds** include funds raised through public deposits, inter-corporate deposits, bank finance, and other sources like Commercial Papers or debentures [1].  
+- **Public deposits** are explicitly defined as funds accepted by a company from the public [1], but public funds are broader.  
+Thus, a company avoiding customer deposits (public deposits) might still use other forms of public funds (e.g., bank finance, inter-corporate deposits) and would need to ensure compliance with regulations governing such activities.</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1739,7 +1685,7 @@
         </is>
       </c>
       <c r="J23" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
@@ -1774,12 +1720,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>No, you cannot stop watching their transactions once a customer's KYC documents are checked. The NBFC must continue monitoring transactions based on risk-based approaches and periodic KYC updation requirements. For example:  
-- **Periodic KYC updation** is mandatory: High-risk customers require updates every 2 years, medium-risk every 8 years, and low-risk every 10 years [3].  
-- **Ongoing transaction limits**: Accounts opened via Aadhaar OTP-based e-KYC must adhere to balance and credit caps (e.g., ₹1 lakh balance, ₹2 lakh annual credit). Exceeding these thresholds triggers account suspension until full CDD is completed [5].  
-- **Suspicious activity monitoring**: If ML/TF risks or high-risk scenarios are detected, the NBFC must re-verify the customer's identity using CDD standards [28].  
-- **Document validity checks**: Even after initial KYC, the NBFC must ensure documents remain valid and match the customer's profile during periodic updates [3][4].  
-Thus, transaction monitoring and KYC compliance are ongoing obligations, not one-time checks.</t>
+          <t>No, once a customer's KYC documents are checked, you cannot stop watching their transactions. The NBFC must continue monitoring transactions for suspicion of ML/TF activities or other high-risk scenarios, as specified in paragraph 28(viii) of the directions [1]. Additionally, periodic KYC updation is mandatory based on risk categories: high-risk customers require updates every two years, medium-risk every eight years, and low-risk every 10 years [6](1). Even low-risk customers must have KYC updated within one year of its due date or by June 30, 2026, whichever is later [6](2). Furthermore, accounts opened via Aadhaar OTP-based e-KYC must undergo identification as per paragraph 23 or 26–27 (V-CIP) within one year, or the account will be restricted or closed [5](6). The NBFC must also ensure that KYC records are incrementally updated and shared with CKYCR, with periodic checks for validity and completeness [4](7).</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1833,7 +1774,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>No, the NBFC cannot onboard someone who insists on using a made-up name for privacy. According to [1] §17(1), the NBFC shall not open any account in an anonymous or fictitious/benami name. Additionally, [1] §17(9) requires verifying that the customer's identity does not match any name in sanctions lists. Using a made-up name would violate these provisions, as it falls under "anonymous" or "fictitious" names, which are explicitly prohibited.</t>
+          <t>No, the NBFC cannot onboard someone who insists on using a made-up name for privacy. According to [1] §17(1), the NBFC shall not open any account in an anonymous or fictitious/benami name. This explicitly prohibits onboarding under pseudonyms or fabricated names, even for privacy reasons. Additionally, if the customer refuses to cooperate with CDD measures (e.g., providing verifiable identity documents), the NBFC must either file an STR [1] §17(2) or deny the account, as per [1] §18.</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1852,7 +1793,7 @@
         </is>
       </c>
       <c r="J25" t="n">
-        <v>6.5</v>
+        <v>6.2</v>
       </c>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
@@ -1887,7 +1828,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>No, sending every borrower an English-only loan letter is not sufficient. The NBFC must communicate in the vernacular language or a language as understood by the borrower [1], [2], [3], and [4]. For illiterate borrowers, important terms and conditions must be explained in the presence of a witness (not an NBFC employee) [3]. Additionally, digitally signed documents (like KFS, sanction letters, etc.) must be in the borrower's chosen language or regional language [4]. English-only communication would violate these requirements unless the borrower explicitly chooses English.</t>
+          <t>No, sending every borrower an English-only loan letter is not sufficient. The passages mandate that communications, including loan terms and conditions, must be in the vernacular language or a language as understood by the borrower [1], [3], [4]. For illiterate borrowers, important terms must be explained in their presence with a witness (not an NBFC employee) [3]. Additionally, loan agreements and key documents must be in a language the borrower understands, with exceptions only for digitally signed documents compliant with the IT Act [4]. English alone does not meet these requirements unless the borrower specifically chooses it.</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1906,7 +1847,7 @@
         </is>
       </c>
       <c r="J26" t="n">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
@@ -1941,7 +1882,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Yes, borrowers must receive copies of all enclosures quoted in the loan agreement. According to [1], NBFCs are required to furnish a copy of the loan agreement **along with a copy each of all enclosures quoted in the loan agreement** to borrowers at the time of sanction/disbursement. This is explicitly stated as a key component to avoid disputes and ensure transparency. Similarly, [2] mandates that a copy of the terms and conditions (including enclosures) must be made available to the borrower. These requirements apply universally, with no exceptions mentioned for specific cases.</t>
+          <t>Yes, borrowers must receive copies of all enclosures quoted in the loan agreement. According to the regulations, an NBFC shall "furnish a copy of the loan agreement along with a copy each of all enclosures quoted in the loan agreement to all the borrowers at the time of sanction/disbursement of loans" [1]. This requirement is reiterated in [2], which mandates that the terms and conditions (including enclosures) must be made available to the borrower. Additionally, [3] specifies that all communication, including terms and conditions, must be in the borrower's understandable language, and [4] confirms that borrowers must refer to the loan and security documents, which include enclosures. Thus, providing copies of all attachments is a statutory obligation.</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -1960,7 +1901,7 @@
         </is>
       </c>
       <c r="J27" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
@@ -1995,7 +1936,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>The Board of the NBFC or HFC should decide how to set lending rates, considering factors such as **cost of funds, margin, and risk premium** [2][6]. They must disclose the interest rate model, gradations of risk, and rationale for different rates to borrowers in the application form and sanction letter [2]. For microfinance loans, the Board must also define an all-inclusive interest rate model with components like cost of funds, risk premium, and margin, along with a ceiling on rates [4]. Additionally, rates must be annualized to ensure clarity for borrowers [2].</t>
+          <t>The Board of the NBFC or HFC should decide how to set lending rates, considering factors such as **cost of funds, margin, and risk premium** [2], [5], [6]. They must also ensure transparency by disclosing the interest rate model, gradations of risk, and rationale for different rates to borrowers in application forms and sanction letters [2]. For microfinance loans, the Board must establish a **ceiling on interest rates and all other charges** [4]. Additionally, the rate must be an **annualised rate** to clarify exact charges to borrowers [2]. The Board’s policy must align with regulatory norms and include objective criteria for fees/charges, avoiding indirect credit enhancement or default guarantees [3].</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -2014,7 +1955,7 @@
         </is>
       </c>
       <c r="J28" t="n">
-        <v>5.5</v>
+        <v>7.2</v>
       </c>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
@@ -2049,12 +1990,8 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Yes, the rationale for charging different interest rates to different categories of borrowers must be explicitly communicated. The NBFC must disclose the rate of interest and the approach for gradations of risk, along with the rationale for charging different rates to different borrowers, in the application form and sanction letter [1]. For credit cards, the interest rates and rationale for differential rates (e.g., based on payment history) must be auditable, publicized on the website, and clearly explained with examples in the Welcome Kit and billing statements [6]. 
-**Conditions and exceptions**:  
-1. The rationale must be disclosed upfront in the loan agreement and key facts statement, and updated if rates change [1][6].  
-2. For floating-rate loans, borrowers must be given options to switch to fixed rates or prepay without discriminatory charges [2].  
-3. Penal charges for defaults must be reasonable, non-discriminatory, and disclosed upfront, but these are separate from interest rate differentiation [3].  
-4. The explanation must include how risk gradations justify rate differences, and annualized rates must be used for transparency [1][4].</t>
+          <t>Yes, the passages require explaining why different borrowers get different interest rates. Specifically, [1] states that the rate of interest and the approach for gradations of risk, along with the "rationale for charging different rate of interest to different categories of borrowers," must be disclosed to the borrower or customer in the application form and communicated explicitly in the sanction letter. This obligation applies to NBFCs when determining interest rates for loans and advances. 
+Other passages do not address this specific requirement for explaining rate differentials.</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -2073,7 +2010,7 @@
         </is>
       </c>
       <c r="J29" t="n">
-        <v>7.8</v>
+        <v>6.5</v>
       </c>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
@@ -2108,7 +2045,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>No, it is not solely the agency's problem. The NBFC/HFC shares responsibility as they must ensure their agents adhere to fair practices, avoid harassment, and comply with due diligence processes [1][3][6]. The NBFC is liable for the actions of its recovery agents, including mistreatment of borrowers, and must enforce training, monitoring, and grievance redressal mechanisms [1][2][4]. Regulatory frameworks hold NBFCs/HFCs accountable for their agents' conduct, including potential supervisory actions or penalties if violations occur [4].</t>
+          <t>If an outside collection agency mistreats a borrower, it is not solely the agency's problem. The NBFC, card issuer, or HFC (depending on the context) shares responsibility. The NBFC must ensure its recovery agents adhere to strict conduct rules, including avoiding intimidation, harassment, and other harsh practices [1][3]. It is also required to train agents, verify their credentials, and provide clear authorisation and contact details to borrowers [1][2]. Additionally, the NBFC must establish grievance redressal mechanisms and monitor agents' compliance with fair practices [1][3][4]. The card issuer is liable for its agents' actions and must ensure they do not engage in misconduct [2]. Thus, the financial institution cannot absolve itself of responsibility by outsourcing recovery efforts.</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -2127,7 +2064,7 @@
         </is>
       </c>
       <c r="J30" t="n">
-        <v>7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
@@ -2162,7 +2099,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>No, the RBI does not require prior approval for every financial-services outsourcing contract. An NBFC may proceed without prior RBI approval, but such arrangements are subject to on-site/offsite monitoring, inspection, and scrutiny by the RBI [1]. The NBFC must ensure compliance with regulatory requirements through written agreements, risk management, and oversight mechanisms, but explicit prior approval from RBI is not mandated for signing contracts.</t>
+          <t>No, the RBI does not require prior approval for every financial-services outsourcing contract. An NBFC can proceed without prior RBI approval, but the arrangement must be subject to RBI's on-site/offsite monitoring, inspection, and scrutiny [1]. The NBFC must ensure the outsourcing agreement is legally vetted, includes risk management provisions, and allows RBI access to information as needed [2][3][5]. RBI's oversight focuses on post-approval monitoring rather than pre-approval mandates.</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -2181,7 +2118,7 @@
         </is>
       </c>
       <c r="J31" t="n">
-        <v>4.8</v>
+        <v>5.8</v>
       </c>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
@@ -2216,7 +2153,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>No, a Credit Information (CI) must submit credit information to all Credit Information Companies (CICs), not just CIBIL. [1] Section 10(1) explicitly mandates that a CI shall submit data to "all CICs." Additionally, [2] Section 12(1) reinforces this by requiring reporting to CICs in the Uniform Credit Reporting Format (UCRF), without restriction to a single CIC. The passages do not permit selective reporting to only one CIC like CIBIL.</t>
+          <t>No, a CI cannot send borrowers' credit information only to CIBIL. According to the guidelines, a CI must submit data to **all CICs** (Credit Information Companies), not selectively to a single CIC like CIBIL [1]. The regulations mandate reporting to all CICs as per the timelines and formats specified, including submitting full files and incremental accounts [1][2]. There is no provision allowing exclusive reporting to one CIC.</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -2235,7 +2172,7 @@
         </is>
       </c>
       <c r="J32" t="n">
-        <v>6.2</v>
+        <v>5.6</v>
       </c>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
@@ -2270,7 +2207,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>No, the deposit product cannot allow customers to demand repayment whenever they want like a savings account. NBFCs are prohibited from accepting public deposits repayable on demand [1]. Premature repayment is only permitted after three months from the deposit date, at the NBFC's discretion [5]. Additionally, repayment terms must specify maturity periods, interest rates, and conditions for renewal, which are fixed and not on-demand [6].</t>
+          <t>No, your deposit product cannot let customers demand repayment whenever they want, as NBFCs are prohibited from accepting public deposits repayable on demand [1]. Repayment terms must adhere to structured conditions, such as permitting premature repayment only after three months from the deposit date [5]. Savings accounts, which typically allow on-demand withdrawals, are explicitly excluded under this regulation.</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -2289,7 +2226,7 @@
         </is>
       </c>
       <c r="J33" t="n">
-        <v>4.7</v>
+        <v>5.6</v>
       </c>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
@@ -2324,12 +2261,12 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>No, for an ordinary loan that has become a Non-Performing Asset (NPA), unpaid interest cannot be booked as income. Income, including interest, on NPA shall be recognized only when it is actually realized. Any such income recognized before the asset became non-performing and remaining unrealized shall be reversed [2]. This applies regardless of the loan type, as the rule is explicitly stated for NPAs in general. 
+          <t>For an ordinary loan that has become an NPA, **unpaid interest cannot be booked as income**. Income on NPA, including interest, is recognized **only when actually realized** [2]. Any income recognized before the asset became non-performing and remaining unrealized must be reversed [2]. This applies regardless of the loan type, as the rule is explicitly tied to NPA classification. 
 **Conditions and exceptions**:  
-- The reversal applies to income recognized prior to the asset becoming NPA but remains unrealized.  
-- For loans with moratoriums, capitalized interest during the moratorium period need not be reversed if the loan becomes NPA post-moratorium [2].  
-- In cases where a resolution plan under RBI Directions, 2025 is implemented, interest income recognition may follow accrual basis for borrower accounts classified as 'Standard' post-resolution [2].  
-- For NBFC-ML, NPA classification is based on 90 days overdue, but income recognition rules for NPAs remain governed by the above [4].</t>
+- If the loan was restructured under Chapter VI-A of the RBI Directions, 2025, and a resolution plan is implemented, income recognition for such accounts may follow accrual basis [2].  
+- For NBFCs with a glide path for NPA norms (e.g., 90-day threshold), the 180-day rule for NPA classification applies only until their respective timelines (March 31, 2024–2026) [1].  
+- If the loan is classified as a **loss asset** (e.g., due to insurance denial, time-barred debt, or defective documentation), income recognition is further restricted under HFC-specific rules [3].  
+Thus, **unpaid interest on NPA must be reversed** unless explicitly allowed under restructuring or resolution plans.</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -2348,7 +2285,7 @@
         </is>
       </c>
       <c r="J34" t="n">
-        <v>7.3</v>
+        <v>8</v>
       </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
@@ -2383,7 +2320,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Yes, a Middle Layer NBFC needs a designated compliance head. Specifically, it must appoint a **Chief Compliance Officer (CCO)** who is sufficiently senior in the organization hierarchy and report to the Board, as mandated by the Board-approved policy [1] and the appointment requirements [6]. The CCO's role includes promoting a compliance culture, ensuring adherence to laws, and overseeing statutory compliance [1][6]. Additionally, the CCO must head the Compliance Department, which must be independent, adequately resourced, and subject to periodic review [3].</t>
+          <t>Yes, a Middle Layer NBFC needs a designated compliance head. According to [1], NBFCs in the Middle Layer or Upper Layer must have a Board-approved policy for the Chief Compliance Officer (CCO), including their role and responsibilities as specified in paragraph 25(2) of the Directions. Additionally, [6] mandates that NBFCs appoint a CCO who is a senior executive reporting to the Board. These requirements apply to Middle Layer NBFCs as they fall under the scope of these regulations [5].</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -2402,7 +2339,7 @@
         </is>
       </c>
       <c r="J35" t="n">
-        <v>5.4</v>
+        <v>6.7</v>
       </c>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
@@ -2437,7 +2374,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>A vendor's promise to recover from an outage is not sufficient for the outsourcing file. The passages mandate specific contractual provisions, such as contingency plans to ensure business continuity [1][5][6], audit rights [1][6], data protection measures [1][5], and legal obligations for the service provider to maintain readiness and preparedness [5][6]. These requirements must be explicitly included in the outsourcing agreement, not merely relied upon as a promise.</t>
+          <t>The vendor's promise alone is not sufficient for the outsourcing file. The passages specify that contingency plans and business continuity measures must be explicitly included in the outsourcing agreement, such as clauses requiring the service provider to ensure testing requirements [1](x), adopt sound business continuity management practices [5](64), and maintain readiness for disruptions [6](vi). Additionally, the NBFC must ensure these provisions are rigorously enforced, including regular audits and compliance with regulatory standards [1](ii), [5](63). A mere promise lacks the enforceability and structural safeguards mandated by the regulations.</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -2456,7 +2393,7 @@
         </is>
       </c>
       <c r="J36" t="n">
-        <v>5.9</v>
+        <v>6.3</v>
       </c>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
@@ -2491,7 +2428,12 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>No, your NBFC-ICC entities cannot both remain in the Base Layer. Under Rule 17 of [1], NBFCs in a group must consolidate their assets. With combined assets of ₹1100 crore (₹600 crore + ₹500 crore), which exceeds the ₹1000 crore threshold, they must be classified in the Middle Layer. NBFC-ICC entities are typically in the Base Layer by default [3], but consolidation triggers Middle Layer classification for the entire group. NBFC-D entities in the group (if any) would instead follow separate regulations [1]. Thus, your NBFC-ICCs must move to the Middle Layer.</t>
+          <t>The NBFC-ICC with ₹600 crore and its sister NBFC-ICC with ₹500 crore cannot both remain in the Base Layer. Under Rule 17 of [1], NBFCs in a group must consolidate their assets. Since their combined assets (₹1100 crore) exceed ₹1000 crore, they are classified in the Middle Layer [1]. NBFC-ICC is explicitly placed in the Base Layer by default only if their standalone asset size is below ₹1000 crore [3]. However, consolidation triggers Middle Layer classification regardless of individual sizes. Thus, both NBFC-ICCs must be governed by Middle Layer regulations. 
+**Conditions and exceptions**:  
+- Consolidation applies only to RBI-registered NBFCs in the group [1].  
+- Unregistered CICs with asset size below ₹100 crore are excluded from consolidation unless they accessed public funds [1].  
+- NBFC-ICC in Middle Layer must comply with Middle Layer regulations, including the Reserve Bank of India (Non-Banking Financial Companies - Acceptance of Public Deposits) Directions, 2025 [1].  
+- NBFC-P2P and NBFC-AA are exempt from consolidation and remain in Base Layer [6].</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -2510,7 +2452,7 @@
         </is>
       </c>
       <c r="J37" t="n">
-        <v>12.8</v>
+        <v>12.2</v>
       </c>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
@@ -2545,12 +2487,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>No, you cannot immediately stop Middle Layer reporting. Once your asset size falls below ₹1,000 crore due to temporary fluctuations, you must continue complying with NBFC-ML reporting requirements and extant directions until the submission of your next audited balance sheet to the Reserve Bank of India (RBI) and receipt of a specific dispensation from the RBI [1]. The RBI may grant relief only after reviewing the next audited balance sheet and confirming the asset size reduction is not permanent. 
-**Conditions and limitations:**  
-1. Temporary asset size drops (e.g., ₹1,050 crore → ₹950 crore) do not exempt you from Middle Layer obligations.  
-2. You must continue reporting as an NBFC-ML until the RBI explicitly dispenses with the requirement.  
-3. The RBI may require additional scrutiny if the asset size remains below ₹1,000 crore for an extended period.  
-4. Consolidation rules in groups (per [1] and [3]) do not apply here, as this is a standalone NBFC-ICC.</t>
+          <t>No, you cannot immediately stop Middle Layer reporting. Once your asset size falls below ₹1,000 crore due to temporary fluctuations, you must continue complying with NBFC-ML reporting requirements and regulations until the submission of your next audited balance sheet to the Reserve Bank of India (RBI) and until a specific dispensation is granted by the RBI [1]. This applies even if the asset size temporarily drops below the threshold.</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -2569,7 +2506,7 @@
         </is>
       </c>
       <c r="J38" t="n">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
@@ -2604,14 +2541,12 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Your NBFC-ICC, classified as Middle Layer (NBFC-ML), is **not capital-compliant**. Here's why:  
-- **Tier 1 Capital Requirement**: NBFC-ML must maintain a minimum Tier 1 capital of **10% of aggregate RWAs** [5](5). Your Tier 1 capital is **9%**, which is below this threshold.  
-- **CRAR Compliance**: Your CRAR of **17%** meets the minimum requirement of **15% of aggregate RWAs** [5](3), but this is secondary to the Tier 1 capital shortfall.  
-**Key Conditions**:  
-1. Tier 1 capital must be **at least 10% of RWAs** for NBFC-ML.  
-2. Tier 2 capital cannot exceed **100% of Tier 1 capital** [5](3), but this does not offset the Tier 1 deficiency.  
-3. CRAR thresholds in [2] (e.g., 15% for NBFC-D/ND) are **irrelevant** here, as your classification as NBFC-ML triggers stricter Tier 1 requirements.  
-Thus, your NBFC fails to meet the Tier 1 capital adequacy norm for Middle Layer entities.</t>
+          <t>The NBFC-ICC is not capital-compliant. 
+**Reasons:**  
+1. **Tier 1 Capital Requirement:** As a Middle Layer NBFC (NBFC-ML), it must maintain a minimum Tier 1 capital of **10% of aggregate RWAs** [5]. The NBFC's Tier 1 capital is **9%**, which is below this threshold.  
+2. **CRAR Compliance:** While the NBFC's CRAR of **17%** exceeds the **15% minimum** for Middle Layer NBFCs [5], this does not offset the Tier 1 capital shortfall.  
+3. **Tier 2 Capital Limit:** Tier 2 capital cannot exceed **100% of Tier 1 capital** [5]. Since Tier 1 is 9%, Tier 2 must also be ≤9%, but this is not directly relevant to the current non-compliance.  
+**Conclusion:** The NBFC fails to meet the Tier 1 capital requirement, rendering it non-compliant despite the CRAR being adequate.</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -2630,7 +2565,7 @@
         </is>
       </c>
       <c r="J39" t="n">
-        <v>10.9</v>
+        <v>12.6</v>
       </c>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
@@ -2665,7 +2600,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>No, you should not continue questioning the customer. If the NBFC forms a suspicion of money laundering or terrorist financing and reasonably believes that performing the CDD process will tip off the customer, it shall not pursue the CDD process and instead file an STR with FIU-IND [1]. This is explicitly stated in section 19 of the Customer Acceptance Policy.</t>
+          <t>If the NBFC forms a suspicion of money laundering or terrorist financing and reasonably believes that performing the CDD process will tip off the customer, it shall **not pursue the CDD process** and instead **file an STR with FIU-IND** [1]. This explicitly prohibits continuing KYC questioning in such cases. The decision to suspend CDD must be based on a reasonable belief that further inquiry would alert the customer, and the NBFC is mandated to report the suspicion via STR instead.</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -2719,7 +2654,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>The loan cannot be upgraded to 'standard' unless all arrears across all credit facilities to the borrower are cleared. Since the borrower has two loans classified as NPA and only one loan's arrears are cleared, the entire borrower's accounts remain NPA under paragraph 25 of [1], which mandates repayment of all arrears for multiple facilities. Additionally, paragraph 23 of [1] treats asset classification as borrower-wise, not facility-wise, meaning all facilities to the borrower are collectively treated as NPA/NPI. Thus, the single loan's upgrade is contingent on full repayment of all arrears across both loans.</t>
+          <t>The loan cannot become standard. According to [1] paragraph 25, for borrowers with more than one credit facility, loan accounts classified as NPA may be upgraded to standard only upon repayment of **entire arrears of interest and principal pertaining to all** credit facilities. Since the borrower has two loans (facilities) and only one's arrears are cleared, the entire arrears across both loans remain unpaid, preventing the upgrade. Additionally, [1] paragraph 24 specifies that NPAs may be upgraded to standard **only if entire arrears** are paid, which is not met here. Thus, the loan remains NPA until all arrears for both facilities are resolved.</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -2738,7 +2673,7 @@
         </is>
       </c>
       <c r="J41" t="n">
-        <v>9.5</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
@@ -2774,12 +2709,11 @@
       <c r="F42" t="inlineStr">
         <is>
           <t>The digital-lending partner's request to receive disbursements in its own pool account and then transfer them to borrowers is **not permitted** under the specified regulations. 
-**Conditions and restrictions:**  
-1. **Escrow account requirement**: Funds from lenders must be transferred to the **Lenders' Escrow Account** (per paragraph 37 of Directions), and disbursements to borrowers must occur **directly from this escrow account** to the borrower's bank account, **not through a pool account** [1].  
-2. **Prohibition on holding funds**: NBFC-P2P entities are explicitly barred from holding funds on their balance sheet, including pool accounts, except for escrow accounts as specified in paragraphs 37 and 38 [3].  
-3. **Cash transactions prohibited**: All fund transfers must occur **through bank accounts**, with **cash transactions strictly prohibited** [1].  
-4. **Specific end-use exceptions**: While direct disbursement to end-beneficiaries is allowed under exceptions (e.g., specific end-use loans), this does not authorize the use of a pool account for intermediate holding [2].  
-Thus, the described mechanism violates the mandated funds transfer mechanism and prudential norms.</t>
+**Key reasons:**  
+1. **Funds Transfer Mechanism:** Disbursements must be made directly to the borrower's bank account from the Borrowers' Escrow Account, not through a pool account. Funds from the Borrowers' Escrow Account are explicitly prohibited for loan disbursement [1].  
+2. **Prohibition on Holding Funds:** NBFC-P2P entities are barred from holding funds received from lenders or borrowers on their balance sheet, except as specified in escrow accounts [3]. A "pool account" would constitute holding funds, which violates this rule.  
+3. **Escrow Account Rules:** All fund transfers must occur through bank accounts, and cash transactions are strictly prohibited [1]. A pool account does not align with the mandated escrow-based mechanism.  
+**Exceptions:** The only permitted exception for direct disbursement is when funds are transferred directly into the end-beneficiary's bank account (not a pool account) [2](iii). Thus, the proposed method involving a pool account is invalid.</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -2798,7 +2732,7 @@
         </is>
       </c>
       <c r="J42" t="n">
-        <v>10.2</v>
+        <v>9.4</v>
       </c>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
@@ -2833,7 +2767,11 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Consent is required but may not be sufficient on its own. According to [2], NBFCs must ensure data collection (including contact lists) is need-based and with explicit borrower consent, with audit trails. However, accessing contact lists for credit scoring beyond KYC purposes (as described in [2][1]) may not be explicitly permitted. Additionally, [3] mandates that consent artefacts must specify the purpose (e.g., "credit scoring") and recipients, and [6] prohibits NBFC-AA from using customer info beyond explicitly requested purposes. Thus, consent alone is insufficient; it must be explicitly tied to the specific purpose (credit scoring), include detailed terms, and comply with the consent artefact requirements.</t>
+          <t>The loan app's request for contact list access to improve credit scoring is **not sufficient** under the provided guidelines. 
+- **Passage [2]** explicitly states that NBFCs must ensure data collection (including mobile phone resources like contact lists) is **need-based** and requires **prior and explicit consent**. However, access to contact lists is restricted to **onboarding/KYC requirements** only. Credit scoring is not explicitly listed as a valid purpose for accessing contact lists. 
+- **Passage [3]** reinforces that financial information sharing requires explicit consent, but this pertains to financial data, not contact lists. 
+- **Passage [2]** also mandates that borrowers must have the option to **revoke consent** and **restrict disclosure** to third parties. 
+Thus, while **explicit consent** is required, the app's use of contact list data for credit scoring may **exceed permissible purposes** unless explicitly authorized under KYC requirements. The consent checkbox alone is insufficient without aligning the access purpose with statutory guidelines. [2]</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -2852,7 +2790,7 @@
         </is>
       </c>
       <c r="J43" t="n">
-        <v>9</v>
+        <v>10.6</v>
       </c>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
@@ -2887,12 +2825,12 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>No, an NBFC (including Middle Layer NBFCs) cannot automatically increase credit limits for customers who repay on time. According to [1] §8.2, an NBFC must ensure there is **no automatic increase in credit limit** unless an **explicit request** is received, evaluated, and documented from the borrower. This rule applies universally to all NBFCs, regardless of their layer classification. 
+          <t>No, you cannot automatically increase credit limits for customers who repay on time. According to [1] §8(2), an NBFC (including Middle Layer NBFCs) shall ensure there is **no automatic increase in credit limit** unless an explicit request is received, evaluated, and kept on record from the borrower. This applies regardless of repayment history. Automatic adjustments are prohibited under this rule. 
 **Conditions and exceptions**:  
-1. **Explicit borrower request**: Any credit limit increase must be based on a **specific, written or authenticated electronic request** from the borrower [1] §8.2.  
-2. **No exceptions for repayment history**: The passages do not permit automatic increases based on repayment behavior or other criteria.  
-3. **Compliance with pre-payment rules**: While Middle Layer NBFCs are exempt from pre-payment charges on loans up to ₹50 lakh [6] §34(2)(ii), this does not override the requirement for explicit borrower consent for credit limit adjustments.  
-Thus, automatic limit increases are prohibited without the borrower's explicit approval.</t>
+- The borrower must explicitly request the credit limit increase.  
+- The NBFC must evaluate and document the request.  
+- No exceptions are provided in the passages for Middle Layer NBFCs or repayment behavior.  
+Thus, automatic limit increases are not permitted.</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -2911,7 +2849,7 @@
         </is>
       </c>
       <c r="J44" t="n">
-        <v>10.5</v>
+        <v>7</v>
       </c>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
@@ -2946,11 +2884,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>No, you cannot outsource the final decision to sanction retail loans because it is explicitly listed as a core management function that shall not be outsourced [1]. This applies regardless of the NBFC's layer (Middle Layer or otherwise). The NBFC retains ultimate control and responsibility for such decisions, including ensuring compliance with KYC norms and loan sanctioning [1][17]. 
-**Conditions and limitations:**  
-1. **Core functions**: Determining compliance with KYC norms for opening deposit accounts, sanctioning loans (including retail loans), and managing investment portfolios are strictly non-outsourcable [1].  
-2. **Group outsourcing exception**: Outsourcing these functions within a group/conglomerate is allowed *only* if the NBFC complies with RBI instructions in paragraphs 45–51 [1], but this does not apply to unrelated vendors.  
-3. **Ultimate accountability**: The NBFC remains responsible for the actions of the service provider, including loan sanctioning decisions [17].</t>
+          <t>No, you cannot outsource the final decision to sanction retail loans to an unrelated fintech vendor. According to [1], core management functions such as "giving sanction for loans (including retail loans)" are explicitly prohibited from being outsourced. This restriction applies regardless of whether the service provider is related or unrelated. The NBFC must retain ultimate control over such decision-making, as stated in [6][17]. Additionally, Middle Layer NBFCs are subject to these restrictions under Chapter IV and IT-specific provisions in Chapter II, which apply to them [2][2].</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -2969,7 +2903,7 @@
         </is>
       </c>
       <c r="J45" t="n">
-        <v>9</v>
+        <v>7.3</v>
       </c>
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr"/>
@@ -3004,7 +2938,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>No, you cannot skip a formal outsourcing agreement even if both companies share the same parent. The passages mandate that NBFCs must have a legally binding written agreement with group entities, identical to those for non-related parties [1], and that such agreements must include specific clauses like confidentiality, audit rights, risk mitigation, and RBI compliance [3][4][5]. The Board must approve policies for outsourcing to group entities, and the agreement must ensure the NBFC retains control and meets regulatory requirements [6].</t>
+          <t>No, you cannot skip a formal outsourcing agreement even if both companies have the same parent. The passages explicitly require NBFCs to enter into legally binding written agreements with group entities, identical to those for non-related parties [1], including provisions for service scope, confidentiality, audit rights, and RBI oversight [3][4][5]. Key requirements like SLAs, risk management frameworks, and termination clauses are mandatory regardless of group affiliation [1][3][4][5]. The parent company's ownership does not exempt the NBFC from these contractual obligations.</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -3023,7 +2957,7 @@
         </is>
       </c>
       <c r="J46" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr"/>
@@ -3058,7 +2992,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>No, it is not allowed. Key Managerial Personnel (KMP) of an NBFC-ML (Middle Layer) cannot hold directorships in another NBFC-ML or NBFC-UL (Upper Layer) entity, except for directorships in NBFCs-BL (Base Layer) [1]. This restriction applies regardless of whether the other NBFC is part of a consolidated group or not. The prohibition explicitly excludes subsidiaries (as per the exception in [1]), but directorships in other Middle Layer NBFCs are prohibited.</t>
+          <t>No, it is not allowed. Key Managerial Personnel (KMP) of an NBFC shall not hold any office (including directorships) in any other NBFC-ML (Middle Layer) or NBFC-UL (Upper Layer), except for directorships in NBFCs-BL (Base Layer) [1]. Since the other NBFC in question is also a Middle Layer NBFC (NBFC-ML), the KMP (CFO) cannot assume directorship there.</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -3077,7 +3011,7 @@
         </is>
       </c>
       <c r="J47" t="n">
-        <v>6.4</v>
+        <v>7.1</v>
       </c>
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr"/>
@@ -3112,7 +3046,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>No, the NBFC cannot renew existing public deposits while seeking an upgrade if its credit rating has been downgraded below the prescribed investment grade. [1] mandates that upon such downgrading, the NBFC must immediately stop accepting fresh deposits and renewing existing ones. Existing deposits are allowed to run off to maturity, and the NBFC must report the situation to the Reserve Bank within fifteen working days. This restriction applies regardless of efforts to upgrade the credit rating.</t>
+          <t>The NBFC cannot renew existing public deposits if its credit rating has been downgraded below the minimum investment grade. According to [1], such an NBFC must immediately stop accepting fresh deposits and renewing existing ones, with existing deposits running off to maturity. This restriction applies regardless of whether the NBFC is seeking an upgrade, as the regulation does not permit renewals during the downgraded state. Additionally, [2] specifies that excess deposits beyond one and one-half times NOF cannot be renewed until the limit is restored, but this is a separate condition from credit rating downgrades. Thus, the downgrade triggers an immediate cessation of renewals.</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -3122,16 +3056,16 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>REVIEW</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>all key figures present (15)</t>
+          <t>none of the expected figures appear (15)</t>
         </is>
       </c>
       <c r="J48" t="n">
-        <v>6.7</v>
+        <v>6.6</v>
       </c>
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr"/>
@@ -3166,13 +3100,12 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>For an ordinary retail term loan, adding a 2% penal interest rate after a missed EMI and compounding it is **not permitted**.  
-**Conditions and restrictions:**  
-1. **Penal charges (including penal interest) cannot be capitalized**: No further interest shall be computed on penal charges, i.e., compounding of penal interest is prohibited [1], [3].  
-2. **Penal charges must be reasonable and non-discriminatory**: The quantum of penal charges must be commensurate with non-compliance and not used as a revenue tool [3].  
-3. **No upper limit specified but intent is discipline, not profit**: While no cap is prescribed, penal charges must align with the intent of encouraging credit discipline, not revenue generation [3].  
-4. **Individual borrowers’ penal charges**: For loans to individual borrowers (like retail loans), penal charges must not exceed those for non-individual borrowers for similar non-compliance [3].  
-Thus, compounding the 2% penal interest would violate the prohibition on capitalizing penal charges [1], [3].</t>
+          <t>For an ordinary retail term loan, adding a 2% penal interest rate after a missed EMI is **permitted**, but **compounding it is prohibited**. 
+- Penal charges (including penal interest) **cannot be capitalized**, i.e., no further interest can be computed on such charges [1][3]. This means the 2% penal interest rate cannot be compounded.  
+- The penal charges must be **reasonable**, **non-discriminatory**, and **disclosed upfront** in the loan agreement and on the NBFC’s website [3].  
+- The NBFC must ensure the penal charges are **not used as a revenue tool** and are **commensurate with non-compliance** of loan terms [3].  
+- Additionally, the structure of penal charges must be **uniform within the same product category** and **irrespective of the borrower’s constitution** [3].  
+Thus, while a 2% penal interest rate is allowed, compounding it violates the prohibition on capitalization of penal charges.</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -3191,7 +3124,7 @@
         </is>
       </c>
       <c r="J49" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr"/>
@@ -3226,14 +3159,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Yes, a Middle Layer NBFC must report the LSP's lending app to the RBI even if it does not own it, as per [1](12957_Credit-Facilities.pdf p.21 — 18. Reporting of DLAs to RBI).  
-**Conditions and requirements:**  
-1. **Mandatory reporting**: The NBFC must report all DLAs **deployed/joined** by them, including those of LSPs, on the RBI's CIMS portal [1](1).  
-2. **Platform participant obligation**: Even if the NBFC acts as a platform participant (e.g., joining the LSP's lending app alongside other lenders), it must report the DLA [1](1).  
-3. **Website disclosure**: The NBFC must ensure the LSP's DLA is linked to its own website, with details of the DLA prominently displayed [1](4)(i) and [1](4)(iv).  
-4. **Non-endorsement clause**: The NBFC must clarify that including the LSP's DLA in its reporting does not imply RBI endorsement [1](6).  
-5. **Compliance with regulations**: The NBFC must verify that the LSP's DLA complies with RBI guidelines on data privacy, grievance redressal, and other statutory requirements [1](4)(iii).  
-**Exceptions**: No exceptions are specified for Middle Layer NBFCs in this context. The reporting obligation applies universally to all NBFCs, regardless of ownership of the DLA.</t>
+          <t>Yes, you must report the LSP's lending app to the RBI. Under **paragraph 18(1)** of the Directions, an NBFC (including Middle Layer NBFCs) must report **all DLAs deployed or joined** by them, whether their own or those of LSPs, on the CIMS portal. This includes apps joined as a platform participant. Additionally, **paragraph 18(4)(i)** requires certification that DLAs (including those of LSPs) have a link to the NBFC's website with borrower-facing details. The reporting obligation applies regardless of ownership, as the NBFC is deemed responsible for ensuring compliance with regulatory requirements. [1]</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -3252,7 +3178,7 @@
         </is>
       </c>
       <c r="J50" t="n">
-        <v>11.4</v>
+        <v>7.7</v>
       </c>
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr"/>
@@ -3287,7 +3213,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>No, an NBFC cannot notify existing borrowers today that a higher contractual rate applies retrospectively from last month. Changes in interest rates or terms must be effected prospectively, as per [1] (section 15) and [5] (paragraph 34(3)), which explicitly state that adjustments to rates or charges must take effect from the date of communication, not retroactively. Additionally, [5] (paragraph 34(9)) prohibits levying charges retrospectively if they were waived earlier. Notifications must be given in the borrower's language [1] and cannot alter past obligations.</t>
+          <t>No, the passages do not permit notifying existing borrowers that a higher contractual rate applies retrospectively from last month. Changes in interest rates and charges must be effected **only prospectively** [1], meaning they take effect from the date of notification, not retroactively. Additionally, any adjustments to rates or charges must be clearly disclosed in the sanction letter and loan agreement [5], and pre-payment charges cannot be applied retrospectively [5]. Retrospective application of higher rates would violate these rules.</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -3306,7 +3232,7 @@
         </is>
       </c>
       <c r="J51" t="n">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr"/>
@@ -3340,7 +3266,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>The provided context passages do not contain any information about SEBI rules related to minimum public shareholding or offer-allocation requirements for NBFCs planning an IPO. The passages focus on topics such as sponsorship of IDF-MFs, public deposits, concentration risk management, and insurance business entry, but none address IPO-specific regulations under SEBI.</t>
+          <t>The provided passages do not contain information about SEBI rules governing minimum public shareholding or offer-allocation requirements for NBFCs planning an IPO. The contexts focus on RBI regulations related to NBFCs (e.g., public deposits, sponsorship of IDF-MFs, concentration risk management, and insurance business entry), but none address SEBI's specific IPO guidelines for NBFCs. For this query, refer directly to SEBI's applicable regulations.</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -3359,7 +3285,7 @@
         </is>
       </c>
       <c r="J52" t="n">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr"/>
@@ -3393,7 +3319,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>The context passages do not specify the exact stock-exchange disclosure deadline for material events under SEBI LODR regulations. Listed NBFCs must comply with the Securities and Exchange Board of India (Listing Obligations and Disclosure Requirements) Regulations, 2015 (as amended), but the passages do not mention specific timelines for such disclosures [5]. Further details would require reference to the LODR Regulations themselves.</t>
+          <t>The passages do not specify the exact stock-exchange disclosure deadline for material events under SEBI LODR. However, they mention that listed NBFCs must comply with SEBI (Listing Obligations and Disclosure Requirements) Regulations, 2015, as amended [5]. Specific deadlines for material events would depend on the provisions of these regulations, which are not detailed in the provided contexts.</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -3412,7 +3338,7 @@
         </is>
       </c>
       <c r="J53" t="n">
-        <v>6.9</v>
+        <v>6</v>
       </c>
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr"/>
@@ -3446,7 +3372,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>The provided context passages do not specify the timing for closing the trading window before quarterly results for listed NBFC employees under insider-trading rules. Insider dealing restrictions are mentioned in [1](#1), but no explicit timeframe or procedural requirement for trading windows is outlined in the passages.</t>
+          <t>The provided passages do not specify the timing for closing trading windows before quarterly results for listed NBFC employees under insider-trading rules. Insider dealing restrictions are mentioned in [1], but no explicit timeline or regulatory requirement for trading windows is outlined in the contexts.</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -3465,7 +3391,7 @@
         </is>
       </c>
       <c r="J54" t="n">
-        <v>6.7</v>
+        <v>6.3</v>
       </c>
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr"/>
@@ -3499,7 +3425,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>The staff must possess the "requisite qualification prescribed by IRDA" to sell insurance as specified persons of a corporate agent [1]. However, the passages do not specify the exact examinations or training programs required to achieve these qualifications. Additionally, there is no mention of mandatory certification processes or training modules beyond the general requirement of IRDA-compliant qualifications.</t>
+          <t>The passages specify that staff involved in insurance agency/broking business must possess the "requisite qualification prescribed by IRDA" [1]. However, they do not explicitly mention specific examinations or training programs required for this qualification. The focus is on ensuring compliance with IRDA regulations rather than detailing the exact nature of staff training or exams.</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -3509,16 +3435,16 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>REVIEW</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>correctly declined to answer</t>
+          <t>answered a question the corpus should not cover - check for invention</t>
         </is>
       </c>
       <c r="J55" t="n">
-        <v>6.2</v>
+        <v>6.3</v>
       </c>
       <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr"/>
@@ -3552,7 +3478,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>The passages do not contain information about the free-look cancellation period for life policies sold through NBFCs.</t>
+          <t>The passages provided do not contain any information regarding the free-look cancellation period for life insurance policies sold through NBFCs.</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -3571,7 +3497,7 @@
         </is>
       </c>
       <c r="J56" t="n">
-        <v>7.9</v>
+        <v>6.7</v>
       </c>
       <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr"/>
@@ -3605,7 +3531,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>The passages do not mention the GST rate applicable to loan-processing fees or the timing for issuing tax invoices. No relevant information is provided in the contexts.</t>
+          <t>The provided passages do not mention the GST rate applicable to loan-processing fees or the specific timing for issuing tax invoices. Therefore, no information can be derived from the given contexts to answer this question.</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -3624,7 +3550,7 @@
         </is>
       </c>
       <c r="J57" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr"/>
@@ -3658,7 +3584,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>The provided context passages do not mention anything about income-tax deductions for provisions created against bad loans. The regulations focus on accounting disclosures, prudential norms, and provisioning requirements under Indian Accounting Standards (IndAS) and Reserve Bank of India (RBI) guidelines, but none address tax treatment or deductibility of such provisions.</t>
+          <t>The passages do not address whether an NBFC can claim an income-tax deduction for provisions created against bad loans. The provided contexts focus on accounting disclosures, prudential norms, provisioning requirements, and regulatory compliance, but none mention tax deductibility or tax treatment of provisions.</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -3677,7 +3603,7 @@
         </is>
       </c>
       <c r="J58" t="n">
-        <v>6.9</v>
+        <v>5.8</v>
       </c>
       <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr"/>
@@ -3711,7 +3637,7 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>The provided context passages do not mention any TDS rate or exemption threshold applicable to interest paid on a resident customer's fixed deposit. The documents focus on deposit terms, interest payment procedures, and asset-liability management, but none address tax deduction at source (TDS) rates or tax exemption thresholds for such interest.</t>
+          <t>The passages provided do not mention any TDS rate or exemption threshold applicable to interest paid on a resident customer's fixed deposit. The contexts focus on deposit agreements, interest payment procedures, and interest rate sensitivity analysis, but they do not address tax deduction at source (TDS) rates or tax exemption thresholds.</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -3730,7 +3656,7 @@
         </is>
       </c>
       <c r="J59" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr"/>
@@ -3764,7 +3690,7 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>The context passages do not specify the Companies Act filing deadlines for AOC-4 financial statements or MGT-7 annual returns. The provided texts mention timelines for audited returns (e.g., five working days from the Auditor's report signing [1], 15 days post-annual general meeting [2][6]), but these are tied to specific regulators (e.g., NHB, RBI) or return types (e.g., DNBS10, FMR) rather than AOC-4 or MGT-7. No direct reference to these forms or their deadlines under the Companies Act is present.</t>
+          <t>The provided context passages do not specify the Companies Act filing deadlines for AOC-4 financial statements or MGT-7 annual returns. The passages mention timelines for audited returns (e.g., five working days under Section 134 of the Companies Act, 2013 [1], and 15-day deadlines for submissions to NHB or RBI [2][6]), but these are for different forms and regulatory bodies. AOC-4 and MGT-7 are not referenced in the provided texts.</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -3783,7 +3709,7 @@
         </is>
       </c>
       <c r="J60" t="n">
-        <v>9.199999999999999</v>
+        <v>6.2</v>
       </c>
       <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr"/>
@@ -3817,7 +3743,7 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>The provided context passages do not contain any information related to calculating Companies Act CSR spending obligations or transferring unspent CSR amounts. The passages focus on definitions for financial instruments, housing finance, liquidity ratios, and loan transfers, but none address CSR requirements or procedures.</t>
+          <t>The provided passages do not address the calculation of Companies Act CSR spending obligations or the transfer of unspent CSR amounts. They focus on definitions related to public deposits, financial disclosures, asset-liability management, and mortgage guarantee companies, but none mention CSR requirements or procedures for unspent amounts.</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -3836,7 +3762,7 @@
         </is>
       </c>
       <c r="J61" t="n">
-        <v>5.7</v>
+        <v>6.9</v>
       </c>
       <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr"/>

--- a/eval/RBI_NBFC_Retrieval_Questions_results_v2.xlsx
+++ b/eval/RBI_NBFC_Retrieval_Questions_results_v2.xlsx
@@ -3435,12 +3435,12 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>REVIEW</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>answered a question the corpus should not cover - check for invention</t>
+          <t>correctly declined to answer</t>
         </is>
       </c>
       <c r="J55" t="n">
